--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-types-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/tester-types-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Kiểm thử hiệu năng cần quy trình bài bản. Load test (mức 10k CCU) kiểm tra khả năng đáp ứng thông thường. Soak test (duy trì tải trong thời gian dài) rất quan trọng để phát hiện lỗi rò rỉ bộ nhớ (Memory leaks) hoặc đầy ổ cứng log. Spike test giả lập giờ cao điểm (ví dụ chuyển khoản nhận lương).</v>
       </c>
       <c r="F2" t="str">
-        <v>Thiết kế kịch bản kiểm thử tải tăng dần (Step-up Load test) lên mốc 10,000 CCU, chạy kiểm thử độ bền (Endurance/Soak test) duy trì trong 12 giờ để kiểm tra rò rỉ bộ nhớ, và chạy kiểm thử đột biến (Spike test) để xem phản hồi của hệ thống khi tải tăng vọt đột ngột — quy trình kiểm thử hiệu năng toàn diện</v>
+        <v>Bỏ qua bước giả lập tải, nén toàn bộ mã nguồn của database và deploy thẳng lên môi trường production chạy thực tế — chạy thực tế rủi ro cực cao</v>
       </c>
       <c r="G2" t="str">
         <v>Sử dụng 10,000 chiếc điện thoại di động vật lý thực tế xếp trên bàn và thuê 10,000 sinh viên cùng nhấn nút chuyển tiền một lúc — giải pháp vật lý bất khả thi</v>
       </c>
       <c r="H2" t="str">
+        <v>Thiết kế kịch bản kiểm thử tải tăng dần (Step-up Load test) lên mốc 10,000 CCU, chạy kiểm thử độ bền (Endurance/Soak test) duy trì trong 12 giờ để kiểm tra rò rỉ bộ nhớ, và chạy kiểm thử đột biến (Spike test) để xem phản hồi của hệ thống khi tải tăng vọt đột ngột — quy trình kiểm thử hiệu năng toàn diện</v>
+      </c>
+      <c r="I2" t="str">
         <v>Chỉ cần chạy thử nghiệm kịch bản với 1 người dùng duy nhất, lấy thời gian phản hồi nhân lên với 10,000 lần — nhân tuyến tính lý thuyết sai lệch</v>
       </c>
-      <c r="I2" t="str">
-        <v>Bỏ qua bước giả lập tải, nén toàn bộ mã nguồn của database và deploy thẳng lên môi trường production chạy thực tế — chạy thực tế rủi ro cực cao</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Trong CI/CD pipeline, tốc độ phản hồi (feedback loop) rất quan trọng. Bắt dev đợi 1-2 tiếng chạy full regression mỗi lần push code sẽ phá vỡ quy trình CI. Chia nhỏ bộ test: PR check chạy nhanh (Smoke/Unit test), còn full test chạy ngầm hàng đêm khi mọi người đã nghỉ là giải pháp tối ưu.</v>
       </c>
       <c r="F3" t="str">
+        <v>Chỉ chạy kiểm thử tự động trên môi trường máy tính cá nhân của Tester và gửi báo cáo qua file chat Skype — chạy test cục bộ</v>
+      </c>
+      <c r="G3" t="str">
         <v>Phân tách test suite thành: Bộ Test khói chạy nhanh (Smoke Test - dưới 5 phút) chạy tự động ở mỗi Pull Request; và Bộ Test hồi quy đầy đủ (Full Regression Suite) chạy tự động hàng đêm (Nightly build) hoặc định kỳ cuối tuần — phân tách bộ test tối ưu CI/CD pipeline</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Cấu hình cho toàn bộ hệ thống tự động chạy lại tất cả 10,000 test case hồi quy chi tiết mỗi khi developer sửa một dấu chấm hoặc dòng comment trong code — chạy test tối đa gây nghẽn pipeline</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Yêu cầu developers không được phép commit code mới quá 1 lần trong một tuần để dành thời gian cho server chạy test tự động — hạn chế dev commit code</v>
       </c>
-      <c r="I3" t="str">
-        <v>Chỉ chạy kiểm thử tự động trên môi trường máy tính cá nhân của Tester và gửi báo cáo qua file chat Skype — chạy test cục bộ</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>SAST (kiểm thử tĩnh) phát hiện lỗi sớm khi viết code (Shift-left), chỉ ra chính xác dòng code bị hổng bảo mật. DAST (kiểm thử động) phát hiện lỗi khi app đã chạy thực tế (như lỗi xác thực, lỗi SSL, cấu hình API Gateway) mà SAST không thể thấy vì code tĩnh không phản ánh bối cảnh chạy thực tế.</v>
       </c>
       <c r="F4" t="str">
+        <v>SAST chỉ chạy được trên hệ điều hành Windows; còn DAST chỉ chạy được trên hệ điều hành Linux — phân loại theo hệ điều hành</v>
+      </c>
+      <c r="G4" t="str">
+        <v>SAST chỉ test giao diện người dùng Frontend; còn DAST chỉ test cơ sở dữ liệu Backend — phân loại theo layer công nghệ</v>
+      </c>
+      <c r="H4" t="str">
         <v>SAST quét mã nguồn từ bên trong (mã nguồn tĩnh) để tìm lỗ hổng lập trình (như SQL Injection, Buffer Overflow); DAST tấn công giả lập từ bên ngoài vào ứng dụng đang chạy để phát hiện lỗi cấu hình, runtime; kết hợp cả hai để bao phủ tối đa lỗ hổng — SAST quét nguồn vs DAST tấn công runtime</v>
       </c>
-      <c r="G4" t="str">
-        <v>SAST chỉ chạy được trên hệ điều hành Windows; còn DAST chỉ chạy được trên hệ điều hành Linux — phân loại theo hệ điều hành</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>SAST hoàn toàn miễn phí; còn DAST bắt buộc phải thuê hacker mũ đen thực hiện bất hợp pháp — phân loại chi phí pháp lý</v>
       </c>
-      <c r="I4" t="str">
-        <v>SAST chỉ test giao diện người dùng Frontend; còn DAST chỉ test cơ sở dữ liệu Backend — phân loại theo layer công nghệ</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +559,10 @@
         <v>Sử dụng phân tích tác động (Impact Analysis) dựa trên bản vẽ kiến trúc hệ thống và sơ đồ luồng dữ liệu (hoặc xem Git diff code change) để xác định các module phụ thuộc trực tiếp và gián tiếp có sử dụng dữ liệu thuế — phân tích tác động khoanh vùng test</v>
       </c>
       <c r="G5" t="str">
+        <v>Chỉ kiểm thử đúng module tính Thuế vừa được sửa, bỏ qua toàn bộ các module bán hàng, mua hàng, tính lương xung quanh — kiểm thử cục bộ rủi ro cao</v>
+      </c>
+      <c r="H5" t="str">
         <v>Yêu cầu lập trình viên tự viết giấy cam kết rằng code mới của họ không làm hỏng bất kỳ chức năng cũ nào — tin tưởng tuyệt đối lập trình viên</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Chỉ kiểm thử đúng module tính Thuế vừa được sửa, bỏ qua toàn bộ các module bán hàng, mua hàng, tính lương xung quanh — kiểm thử cục bộ rủi ro cao</v>
       </c>
       <c r="I5" t="str">
         <v>Chạy ngẫu nhiên một số test case bất kỳ trong kho dữ liệu mà không cần quan tâm đến tính liên quan của tính năng — chọn test case ngẫu nhiên</v>
@@ -594,10 +594,10 @@
         <v>Để đảm bảo phần mềm tự động nén kích thước cơ sở dữ liệu xuống nhỏ hơn 100MB khi có động đất xảy ra — nén dữ liệu khi thiên tai</v>
       </c>
       <c r="H6" t="str">
+        <v>Để bắt buộc lập trình viên phải sao lưu mã nguồn code ra đĩa mềm vật lý và cất trong két sắt an toàn — sao lưu đĩa mềm vật lý</v>
+      </c>
+      <c r="I6" t="str">
         <v>Để kiểm tra xem hệ thống có tự động gửi tin nhắn SMS chúc mừng sinh nhật cho toàn bộ ban giám đốc ngân hàng hay không — tính năng phụ</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Để bắt buộc lập trình viên phải sao lưu mã nguồn code ra đĩa mềm vật lý và cất trong két sắt an toàn — sao lưu đĩa mềm vật lý</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -623,13 +623,13 @@
         <v>Tách biệt kịch bản test (test logic) ra khỏi dữ liệu test (test data); lưu trữ hàng trăm cặp giá trị đầu vào và kết quả mong đợi trong một file Excel/CSV bên ngoài để script test tự động đọc và chạy lặp lại — tách biệt kịch bản và dữ liệu test</v>
       </c>
       <c r="G7" t="str">
-        <v>Hardcode trực tiếp cả 100 giá trị kiểm thử khác nhau vào bên trong 100 hàm kiểm thử độc lập của mã nguồn code test — hardcode dữ liệu test</v>
+        <v>Xóa bỏ toàn bộ các kịch bản test và chỉ thực hiện test thủ công bằng cách tự gõ tay các giá trị ngẫu nhiên vào form giao diện — thủ công hoàn toàn</v>
       </c>
       <c r="H7" t="str">
         <v>Yêu cầu lập trình viên viết code tự động sinh ra các con số tuổi và giới tính ngẫu nhiên khi chạy chương trình — sinh số ngẫu nhiên</v>
       </c>
       <c r="I7" t="str">
-        <v>Xóa bỏ toàn bộ các kịch bản test và chỉ thực hiện test thủ công bằng cách tự gõ tay các giá trị ngẫu nhiên vào form giao diện — thủ công hoàn toàn</v>
+        <v>Hardcode trực tiếp cả 100 giá trị kiểm thử khác nhau vào bên trong 100 hàm kiểm thử độc lập của mã nguồn code test — hardcode dữ liệu test</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>Điện thoại di động là môi trường tương tác năng động, liên tục bị ngắt. Interrupt testing kiểm tra xem app của bạn có bị crash, bị mất dữ liệu đang nhập dở, hoặc bị treo cứng khi có cuộc gọi điện thoại chen ngang hay không, đảm bảo trải nghiệm người dùng mượt mà.</v>
       </c>
       <c r="F8" t="str">
+        <v>Để bắt buộc người dùng phải cắm sạc điện thoại thì mới cho phép mở ứng dụng sử dụng — bắt buộc cắm sạc</v>
+      </c>
+      <c r="G8" t="str">
         <v>Để đánh giá xem ứng dụng xử lý mượt mà thế nào khi có các ngắt hệ thống đột ngột (cuộc gọi đến, tin nhắn SMS, mất kết nối mạng, pin yếu, cắm sạc) và khôi phục đúng trạng thái trước khi bị ngắt — kiểm thử khả năng xử lý ngắt hệ thống di động</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Để đảm bảo phần mềm tự động chặn toàn bộ các cuộc gọi điện thoại của người dùng khi họ đang mở ứng dụng — chặn cuộc gọi di động</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>Để kiểm tra xem ứng dụng có tự động xóa các file ảnh cũ lưu trong thẻ nhớ điện thoại của khách hàng hay không — tự động xóa ảnh thẻ nhớ</v>
       </c>
-      <c r="I8" t="str">
-        <v>Để bắt buộc người dùng phải cắm sạc điện thoại thì mới cho phép mở ứng dụng sử dụng — bắt buộc cắm sạc</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Testing Pyramid của Mike Cohn nhấn mạnh hiệu quả tài chính và thời gian. Unit tests (đáy) chạy chỉ vài mili-giây, giúp dev phát hiện lỗi lập trình ngay lập tức. UI tests (đỉnh) đi qua toàn bộ các tầng nên chạy rất chậm, tốn tài nguyên và dễ gãy (brittle) khi có một thay đổi nhỏ về giao diện, vì vậy chỉ nên dùng để test các luồng nghiệp vụ cốt lõi nhất (End-to-End).</v>
       </c>
       <c r="F9" t="str">
+        <v>Vì Unit Test do robot tự động viết; còn UI Test bắt buộc phải thuê con người chạy thủ công hoàn toàn — robot vs con người</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Vì giao diện người dùng UI không quan trọng đối với sự thành công của sản phẩm phần mềm — UI không quan trọng</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Vì hệ điều hành máy chủ chỉ hỗ trợ chạy Unit Test chứ không hỗ trợ hiển thị giao diện đồ họa — giới hạn máy chủ</v>
+      </c>
+      <c r="I9" t="str">
         <v>Vì Unit Test chạy cực nhanh, chi phí viết/chạy rẻ và cô lập lỗi dễ dàng; UI Test chạy chậm, chi phí cao, dễ bị lỗi ảo (flaky test) do thay đổi giao diện nên cần hạn chế — tối ưu chi phí và tốc độ phản hồi của bộ test</v>
       </c>
-      <c r="G9" t="str">
-        <v>Vì Unit Test do robot tự động viết; còn UI Test bắt buộc phải thuê con người chạy thủ công hoàn toàn — robot vs con người</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Vì giao diện người dùng UI không quan trọng đối với sự thành công của sản phẩm phần mềm — UI không quan trọng</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Vì hệ điều hành máy chủ chỉ hỗ trợ chạy Unit Test chứ không hỗ trợ hiển thị giao diện đồ họa — giới hạn máy chủ</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Chạy kiểm thử so sánh dữ liệu (Data Comparison): Sử dụng các kịch bản so sánh từng trường dữ liệu giữa bảng nguồn và bảng đích, chạy song song hai hệ thống (Parallel execution) để đối chiếu kết quả đầu ra của cùng một nghiệp vụ — so sánh dữ liệu và chạy song song</v>
       </c>
       <c r="G10" t="str">
+        <v>Yêu cầu lập trình viên tự viết code tự động sinh dữ liệu ảo nạp đầy vào hệ thống mới để chạy thử — sinh dữ liệu ảo</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Chỉ cần chạy thử nghiệm hệ thống mới với 10 dòng dữ liệu mẫu tự gõ bằng tay trên màn hình — test mẫu thủ công đơn giản</v>
+      </c>
+      <c r="I10" t="str">
         <v>Xóa bỏ toàn bộ cơ sở dữ liệu của hệ thống cũ và chỉ kiểm tra xem hệ thống mới có hiển thị giao diện đẹp hay không — xóa database cũ</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Yêu cầu lập trình viên tự viết code tự động sinh dữ liệu ảo nạp đầy vào hệ thống mới để chạy thử — sinh dữ liệu ảo</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Chỉ cần chạy thử nghiệm hệ thống mới với 10 dòng dữ liệu mẫu tự gõ bằng tay trên màn hình — test mẫu thủ công đơn giản</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>Bản địa hóa (Localization) không chỉ là dịch chữ. Nó liên quan đến: định dạng ngày tháng (23/06/2026 vs 06/23/2026), định dạng số (1.000,50 vs 1,000.50), biểu tượng tiền tệ. Hơn nữa, chữ tiếng Đức/tiếng Việt thường dài hơn tiếng Anh khoảng 30%, nếu thiết kế layout UI không linh hoạt sẽ bị lỗi tràn chữ, vỡ khung (Text clipping).</v>
       </c>
       <c r="F11" t="str">
+        <v>Để đảm bảo mã nguồn code của lập trình viên được dịch hoàn toàn sang ngôn ngữ của nước đó — dịch mã nguồn code</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Để ngăn chặn người dùng ở nước khác truy cập vào ứng dụng di động của công ty — chặn người dùng nước ngoài</v>
+      </c>
+      <c r="H11" t="str">
         <v>Để đảm bảo phần mềm hiển thị đúng ngôn ngữ địa phương, đúng định dạng ngày tháng/tiền tệ/số, phù hợp văn hóa và không bị lỗi vỡ khung giao diện (UI clipping) do độ dài chữ khác nhau — bản địa hóa trải nghiệm người dùng</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>Để tự động đổi múi giờ của máy chủ vật lý về múi giờ của thủ đô nước đó — đổi múi giờ máy chủ</v>
       </c>
-      <c r="H11" t="str">
-        <v>Để ngăn chặn người dùng ở nước khác truy cập vào ứng dụng di động của công ty — chặn người dùng nước ngoài</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Để đảm bảo mã nguồn code của lập trình viên được dịch hoàn toàn sang ngôn ngữ của nước đó — dịch mã nguồn code</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
